--- a/data/output/待复核名单_20260622.xlsx
+++ b/data/output/待复核名单_20260622.xlsx
@@ -413,352 +413,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>异常ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>关联单号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>严重程度</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>异常类型</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>异常描述</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>门店ID</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>发现时间</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>处理状态</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>处理意见</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>详细信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ORD000002</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>超消费次数</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>已消费次数(2.0)大于购买次数(1)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>{'order_id': 'ORD000002', 'item_name': '双眼皮手术', 'purchased': 1, 'consumed': 2.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ORD000006</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>超消费次数</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>已消费次数(4.0)大于购买次数(3)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>{'order_id': 'ORD000006', 'item_name': '热玛吉', 'purchased': 3, 'consumed': 4.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ORD000008</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>超消费次数</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>已消费次数(3.0)大于购买次数(2)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>{'order_id': 'ORD000008', 'item_name': '光子嫩肤', 'purchased': 2, 'consumed': 3.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ORD000011</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>超消费次数</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>已消费次数(2.0)大于购买次数(1)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>{'order_id': 'ORD000011', 'item_name': '双眼皮手术', 'purchased': 1, 'consumed': 2.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ORD000019</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>超消费次数</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>已消费次数(4.0)大于购买次数(3)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>S003</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>{'order_id': 'ORD000019', 'item_name': '光子嫩肤', 'purchased': 3, 'consumed': 4.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RF000002</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>退款超剩余价值</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>退款数量(2.0)超过剩余数量(1.00)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>{'refund_id': 'RF000002', 'item_name': '双眼皮手术', 'refund_quantity': 2.0, 'remaining_quantity': 1, 'remaining_amount': 7480.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RF000003</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>退款超剩余价值</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>退款数量(3.0)超过剩余数量(2.00)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>S002</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>{'refund_id': 'RF000003', 'item_name': '水光针', 'refund_quantity': 3.0, 'remaining_quantity': 2, 'remaining_amount': 1666.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RF000005</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>退款超剩余价值</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>退款数量(2.0)超过剩余数量(1.00)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>S001</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2026-06-22 07:44:27</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>{'refund_id': 'RF000005', 'item_name': '水光针', 'refund_quantity': 2.0, 'remaining_quantity': 1, 'remaining_amount': 833.0}</t>
         </is>
       </c>
     </row>
